--- a/04_DESIGN_TABLES/DesignTable_5405.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5405.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2123,24 +2128,47 @@
           <t>5405-04-02</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.405</v>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>5405-04-02</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/8-27 NPTF</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-02 col "L LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 227.5, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-02 col "C HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 227.5, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 227.5, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2151,6 +2179,11 @@
       <c r="N31" t="inlineStr">
         <is>
           <t>5405-04-02</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2160,24 +2193,47 @@
           <t>5405-04-12</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.05</v>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>5405-04-12</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1/4-18 x 3/4-14 NPTF</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-12 col "L LGTH" = "1.74" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 267.8, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-12 col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 267.8, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-04-12 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 267.8, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2188,6 +2244,11 @@
       <c r="N32" t="inlineStr">
         <is>
           <t>5405-04-12</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2197,24 +2258,47 @@
           <t>5405-08-04</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>5405-08-04</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/4-18 NPTF</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-08-04 col "L LGTH" = "1.640" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 338.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-08-04 col "C HEX" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 338.4, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-08-04 col "A1 DRILL" = "0.531" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 338.4, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[8] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2225,6 +2309,11 @@
       <c r="N33" t="inlineStr">
         <is>
           <t>5405-08-04</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2271,24 +2360,47 @@
           <t>5405-20-20</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.66</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>5405-20-20</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 x 1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-20-20 col "L LGTH" = "2.49" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 509.8, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-20-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 509.8, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-20-20 col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 509.8, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[20] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.48, FPT_P1 1.16 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2299,6 +2411,11 @@
       <c r="N35" t="inlineStr">
         <is>
           <t>5405-20-20</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2345,24 +2462,47 @@
           <t>5405-24-20</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.66</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>5405-24-20</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 x 1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-24-20 col "L LGTH" = "2.540" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 540.0, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 22/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5405-08-06 1.87 vs 1.66); CHEX@HEX: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-24-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 540.0, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-08-16 1.38 vs 1.625); D@BORE: Brennan TFA catalog p12 table TFA-p012-t02 "5405 MP-FP STRAIGHT EXPANDER" row 5405-24-20 col "A1 DRILL" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 540.0, page verified) [Brennan = yes 2026-10-18] - male-end bore (to the pocket); mapping: TFA p12 5405 drawing: L = overall, C HEX = body hex, A1 DRILL = male-end bore = SPEC 5405 bore D (impact/F2b.json, certain); same-table check on today's base: 27/28 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5405-16-08 0.94 vs 0.697); TAPDRILL@BORE: end library gen_straight2 FPT[20] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.48, FPT_P1 1.16 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5405 rows</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / D from the Brennan TFA catalog p12 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2373,6 +2513,11 @@
       <c r="N37" t="inlineStr">
         <is>
           <t>5405-24-20</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
